--- a/data/trans_dic/P16A10-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,05</t>
+          <t>2,99; 7,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,43</t>
+          <t>3,56; 8,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,21</t>
+          <t>3,5; 8,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,6</t>
+          <t>3,21; 6,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,95</t>
+          <t>1,96; 6,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,9</t>
+          <t>2,84; 7,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,75</t>
+          <t>1,48; 3,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,26</t>
+          <t>2,99; 6,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,26</t>
+          <t>2,3; 5,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,22</t>
+          <t>3,84; 7,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,82</t>
+          <t>2,71; 4,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,25</t>
+          <t>1,99; 6,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,48</t>
+          <t>2,19; 6,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,14</t>
+          <t>2,98; 7,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,68</t>
+          <t>3,28; 6,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,82</t>
+          <t>0,63; 4,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,24</t>
+          <t>0,57; 4,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,9</t>
+          <t>0,92; 2,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,02</t>
+          <t>1,57; 4,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,17</t>
+          <t>1,3; 3,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,0</t>
+          <t>2,14; 4,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,55</t>
+          <t>2,48; 4,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,47</t>
+          <t>4,44; 8,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,16</t>
+          <t>4,23; 8,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,63</t>
+          <t>5,1; 9,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,93</t>
+          <t>1,71; 8,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,14</t>
+          <t>1,25; 7,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,76</t>
+          <t>1,7; 6,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,98</t>
+          <t>2,23; 10,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 12,34</t>
+          <t>4,15; 12,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,38</t>
+          <t>3,89; 7,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,04</t>
+          <t>4,06; 7,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,91</t>
+          <t>4,73; 8,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,8</t>
+          <t>2,05; 7,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,77</t>
+          <t>5,86; 8,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,28</t>
+          <t>4,55; 7,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,54</t>
+          <t>5,74; 8,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,7</t>
+          <t>5,73; 8,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,97</t>
+          <t>2,8; 5,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,16</t>
+          <t>1,84; 4,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,16</t>
+          <t>2,32; 5,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,07</t>
+          <t>1,4; 4,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 7,32</t>
+          <t>5,07; 7,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,8</t>
+          <t>3,79; 5,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,69</t>
+          <t>4,65; 6,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,12</t>
+          <t>3,52; 6,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,95</t>
+          <t>3,48; 8,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,38</t>
+          <t>3,88; 8,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,05</t>
+          <t>5,34; 9,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,12</t>
+          <t>4,44; 8,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,82</t>
+          <t>4,48; 8,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,52</t>
+          <t>6,46; 10,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,58</t>
+          <t>4,13; 7,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,15</t>
+          <t>4,9; 8,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,63</t>
+          <t>4,43; 7,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 8,9</t>
+          <t>6,02; 9,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,65</t>
+          <t>4,96; 7,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,8</t>
+          <t>5,23; 7,72</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,0</t>
+          <t>0,73; 5,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,67</t>
+          <t>5,78; 8,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,98</t>
+          <t>5,03; 7,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,99</t>
+          <t>6,41; 10,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,26</t>
+          <t>7,27; 10,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,08</t>
+          <t>4,66; 7,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,76</t>
+          <t>4,27; 6,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,92</t>
+          <t>5,04; 7,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,92</t>
+          <t>5,42; 8,02</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,28</t>
+          <t>4,72; 6,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,11</t>
+          <t>4,54; 6,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,02</t>
+          <t>5,23; 6,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,13</t>
+          <t>4,13; 6,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,11</t>
+          <t>4,47; 6,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,53</t>
+          <t>4,0; 5,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,3</t>
+          <t>4,61; 6,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,03; 5,72</t>
+          <t>4,04; 5,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,87</t>
+          <t>4,82; 5,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,54</t>
+          <t>4,49; 5,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 6,31</t>
+          <t>5,16; 6,24</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,73</t>
+          <t>4,4; 5,73</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13555; 33392</t>
+          <t>14186; 33957</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15150; 36865</t>
+          <t>15564; 35516</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15602; 35222</t>
+          <t>15035; 35331</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16508; 33329</t>
+          <t>16233; 32579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6608; 21311</t>
+          <t>6015; 21013</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7107</t>
+          <t>0; 7261</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10582; 27406</t>
+          <t>9848; 27631</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6809; 16767</t>
+          <t>6628; 16858</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24054; 48836</t>
+          <t>23317; 49265</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17067; 39555</t>
+          <t>17259; 38533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28796; 56066</t>
+          <t>29819; 56254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26758; 45923</t>
+          <t>25792; 46323</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7247; 22947</t>
+          <t>7293; 22032</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8838; 27027</t>
+          <t>9138; 28097</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10934; 26929</t>
+          <t>11247; 28279</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14974; 30213</t>
+          <t>14841; 30199</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2345; 14197</t>
+          <t>2355; 15144</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9871</t>
+          <t>0; 9276</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2243; 15779</t>
+          <t>2117; 15664</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3373; 11103</t>
+          <t>3507; 10724</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11643; 29699</t>
+          <t>11627; 30145</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10777; 31432</t>
+          <t>9791; 29789</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16225; 37460</t>
+          <t>16028; 36550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20546; 38010</t>
+          <t>20741; 38149</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24000; 45937</t>
+          <t>24088; 45296</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26745; 51110</t>
+          <t>26473; 51234</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25991; 50242</t>
+          <t>26637; 49479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10230; 52993</t>
+          <t>11407; 53719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2051; 11983</t>
+          <t>2098; 12399</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5134; 17430</t>
+          <t>4373; 17449</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3522; 16579</t>
+          <t>3709; 17477</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6558; 20602</t>
+          <t>6925; 20065</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28533; 52425</t>
+          <t>27602; 52053</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34918; 62236</t>
+          <t>35933; 62461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33518; 61292</t>
+          <t>32510; 58808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16339; 65173</t>
+          <t>17089; 63595</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74463; 108645</t>
+          <t>72515; 108150</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53844; 84335</t>
+          <t>52646; 85251</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63401; 98165</t>
+          <t>65950; 100725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60551; 90025</t>
+          <t>59290; 89350</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20400; 42633</t>
+          <t>19997; 41780</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13876; 31930</t>
+          <t>14130; 32788</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19653; 42589</t>
+          <t>19129; 42193</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13701; 39763</t>
+          <t>13729; 41011</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100236; 142843</t>
+          <t>98904; 141870</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72191; 111660</t>
+          <t>72944; 111098</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91718; 132205</t>
+          <t>91836; 134462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71098; 123221</t>
+          <t>70787; 125236</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11994; 27775</t>
+          <t>12171; 28215</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20782; 42764</t>
+          <t>19833; 41944</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31885; 56159</t>
+          <t>33152; 57849</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20214; 38504</t>
+          <t>21051; 38826</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25405; 50149</t>
+          <t>25465; 48537</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49496; 80035</t>
+          <t>49127; 80622</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29309; 55939</t>
+          <t>30519; 56492</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40006; 68295</t>
+          <t>41064; 68876</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41062; 70049</t>
+          <t>40698; 69622</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76981; 113114</t>
+          <t>76511; 115266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69196; 103924</t>
+          <t>67430; 103627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69311; 102412</t>
+          <t>68624; 101335</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4401</t>
+          <t>0; 4458</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1024; 13302</t>
+          <t>1931; 14227</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2019</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3776</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>71106; 108322</t>
+          <t>72202; 108908</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54818; 88192</t>
+          <t>55602; 87956</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69607; 108098</t>
+          <t>69379; 109200</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55269; 78022</t>
+          <t>55297; 78751</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>73051; 109512</t>
+          <t>72114; 110209</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58842; 92651</t>
+          <t>58617; 92796</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69671; 108482</t>
+          <t>68948; 108126</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55119; 79267</t>
+          <t>54199; 80247</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>152843; 205379</t>
+          <t>154459; 205429</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>154657; 208551</t>
+          <t>155126; 207819</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177698; 237627</t>
+          <t>177088; 230895</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>137407; 206729</t>
+          <t>139296; 205510</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>152830; 206410</t>
+          <t>150846; 205855</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>144181; 195838</t>
+          <t>141850; 194399</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>164193; 222622</t>
+          <t>162972; 222700</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>143902; 204265</t>
+          <t>144468; 203895</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>320922; 390019</t>
+          <t>320501; 391359</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>311777; 385645</t>
+          <t>312392; 385773</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>356248; 436725</t>
+          <t>356596; 431298</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>307553; 397936</t>
+          <t>305640; 398063</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A10-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,17</t>
+          <t>3,1; 7,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,12</t>
+          <t>3,56; 8,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,23</t>
+          <t>3,69; 8,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,45</t>
+          <t>3,81; 7,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,85</t>
+          <t>2,04; 6,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,96</t>
+          <t>2,96; 7,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,77</t>
+          <t>1,65; 3,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,31</t>
+          <t>3,08; 6,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,13</t>
+          <t>2,32; 5,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,25</t>
+          <t>3,92; 7,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,86</t>
+          <t>3,08; 5,13</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,0</t>
+          <t>1,76; 6,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,74</t>
+          <t>2,06; 6,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,5</t>
+          <t>2,79; 7,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,68</t>
+          <t>3,32; 6,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,07</t>
+          <t>0,64; 3,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,21</t>
+          <t>0,58; 3,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,8</t>
+          <t>0,88; 2,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,08</t>
+          <t>1,59; 4,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,95</t>
+          <t>1,41; 4,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,88</t>
+          <t>2,12; 4,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,57</t>
+          <t>2,48; 4,47</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,35</t>
+          <t>4,44; 8,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,18</t>
+          <t>4,32; 8,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,48</t>
+          <t>4,92; 9,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,04</t>
+          <t>5,4; 9,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,39</t>
+          <t>1,68; 7,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,76</t>
+          <t>1,7; 7,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,52</t>
+          <t>2,15; 10,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 12,02</t>
+          <t>4,24; 13,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,33</t>
+          <t>4,08; 7,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 7,06</t>
+          <t>3,96; 7,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,55</t>
+          <t>4,85; 8,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,61</t>
+          <t>5,38; 9,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,73</t>
+          <t>5,89; 8,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,36</t>
+          <t>4,54; 7,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,76</t>
+          <t>5,58; 8,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,63</t>
+          <t>5,78; 8,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,85</t>
+          <t>2,85; 5,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,28</t>
+          <t>1,8; 4,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,11</t>
+          <t>2,46; 5,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,2</t>
+          <t>2,68; 4,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,27</t>
+          <t>5,03; 7,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,77</t>
+          <t>3,72; 5,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,81</t>
+          <t>4,65; 6,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,22</t>
+          <t>4,63; 6,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,07</t>
+          <t>3,17; 7,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,21</t>
+          <t>4,09; 8,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,32</t>
+          <t>5,19; 9,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,19</t>
+          <t>3,93; 7,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,53</t>
+          <t>4,48; 8,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,6</t>
+          <t>6,38; 10,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,65</t>
+          <t>4,03; 7,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 8,22</t>
+          <t>6,34; 9,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,58</t>
+          <t>4,66; 7,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,07</t>
+          <t>5,88; 8,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,63</t>
+          <t>5,06; 7,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,72</t>
+          <t>5,7; 7,69</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,35</t>
+          <t>0,41; 5,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,72</t>
+          <t>5,74; 8,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 7,96</t>
+          <t>4,92; 7,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,09</t>
+          <t>6,27; 9,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,36</t>
+          <t>7,1; 10,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,12</t>
+          <t>4,69; 7,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 6,77</t>
+          <t>4,24; 6,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,9</t>
+          <t>5,06; 8,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,02</t>
+          <t>5,5; 8,08</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,28</t>
+          <t>4,69; 6,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,09</t>
+          <t>4,57; 6,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,82</t>
+          <t>5,22; 6,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,09</t>
+          <t>5,05; 6,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,09</t>
+          <t>4,64; 6,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,49</t>
+          <t>4,09; 5,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,31</t>
+          <t>4,65; 6,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,71</t>
+          <t>4,93; 6,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,82; 5,89</t>
+          <t>4,85; 5,91</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,54</t>
+          <t>4,52; 5,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 6,24</t>
+          <t>5,09; 6,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,73</t>
+          <t>5,1; 6,04</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>28563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10944</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34707</t>
+          <t>41173</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14186; 33957</t>
+          <t>14693; 33220</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15564; 35516</t>
+          <t>15543; 36849</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15035; 35331</t>
+          <t>15822; 36370</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16233; 32579</t>
+          <t>20972; 39106</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6015; 21013</t>
+          <t>6242; 21066</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7261</t>
+          <t>0; 7612</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9848; 27631</t>
+          <t>10274; 26694</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6628; 16858</t>
+          <t>8057; 19231</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23317; 49265</t>
+          <t>24061; 48943</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17259; 38533</t>
+          <t>17440; 38454</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29819; 56254</t>
+          <t>30458; 57604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25792; 46323</t>
+          <t>32052; 53307</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28394</t>
+          <t>30427</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7293; 22032</t>
+          <t>6455; 22654</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9138; 28097</t>
+          <t>8582; 26664</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11247; 28279</t>
+          <t>10507; 27137</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14841; 30199</t>
+          <t>16039; 31390</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2355; 15144</t>
+          <t>2396; 14122</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9276</t>
+          <t>0; 9497</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2117; 15664</t>
+          <t>2145; 14165</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3507; 10724</t>
+          <t>3720; 12012</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11627; 30145</t>
+          <t>11780; 30831</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9791; 29789</t>
+          <t>10596; 31599</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16028; 36550</t>
+          <t>15910; 37119</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20741; 38149</t>
+          <t>22475; 40481</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>33912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42151</t>
+          <t>46959</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24088; 45296</t>
+          <t>24091; 45438</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26473; 51234</t>
+          <t>27068; 50853</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26637; 49479</t>
+          <t>25702; 49845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11407; 53719</t>
+          <t>25464; 44973</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2098; 12399</t>
+          <t>2813; 12836</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4373; 17449</t>
+          <t>4395; 18426</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3709; 17477</t>
+          <t>3571; 17005</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6925; 20065</t>
+          <t>7949; 24948</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27602; 52053</t>
+          <t>28951; 52269</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35933; 62461</t>
+          <t>34979; 63060</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32510; 58808</t>
+          <t>33381; 60114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17089; 63595</t>
+          <t>35437; 61036</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73706</t>
+          <t>78744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>30806</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>102068</t>
+          <t>109550</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72515; 108150</t>
+          <t>72896; 107518</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52646; 85251</t>
+          <t>52621; 84040</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65950; 100725</t>
+          <t>64130; 100006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>59290; 89350</t>
+          <t>65388; 97109</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19997; 41780</t>
+          <t>20334; 41508</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14130; 32788</t>
+          <t>13777; 32006</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19129; 42193</t>
+          <t>20290; 42617</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13729; 41011</t>
+          <t>23083; 40252</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98904; 141870</t>
+          <t>98122; 139598</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72944; 111098</t>
+          <t>71696; 108257</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91836; 134462</t>
+          <t>91807; 134285</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>70787; 125236</t>
+          <t>92251; 128671</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28747</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55865</t>
+          <t>62396</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84612</t>
+          <t>92698</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12171; 28215</t>
+          <t>11078; 27839</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19833; 41944</t>
+          <t>20861; 42178</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33152; 57849</t>
+          <t>32214; 57183</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21051; 38826</t>
+          <t>22272; 40885</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25465; 48537</t>
+          <t>25472; 49457</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49127; 80622</t>
+          <t>48504; 79257</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30519; 56492</t>
+          <t>29773; 56229</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41064; 68876</t>
+          <t>52558; 74964</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40698; 69622</t>
+          <t>42763; 71148</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76511; 115266</t>
+          <t>74762; 112433</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67430; 103627</t>
+          <t>68827; 104032</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>68624; 101335</t>
+          <t>79634; 107341</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>65859</t>
+          <t>72409</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>66870</t>
+          <t>73435</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 4663</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1931; 14227</t>
+          <t>1087; 13733</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 3241</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>72202; 108908</t>
+          <t>71642; 108825</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55602; 87956</t>
+          <t>54411; 86834</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69379; 109200</t>
+          <t>67897; 108015</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55297; 78751</t>
+          <t>59838; 86454</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72114; 110209</t>
+          <t>72478; 108663</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58617; 92796</t>
+          <t>58199; 91793</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68948; 108126</t>
+          <t>69235; 109547</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>54199; 80247</t>
+          <t>59360; 87253</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>179810</t>
+          <t>196030</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>178992</t>
+          <t>198212</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>358802</t>
+          <t>394242</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>154459; 205429</t>
+          <t>153384; 203921</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>155126; 207819</t>
+          <t>155917; 211005</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>177088; 230895</t>
+          <t>176609; 232501</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>139296; 205510</t>
+          <t>173872; 221295</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>150846; 205855</t>
+          <t>156653; 209153</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>141850; 194399</t>
+          <t>145000; 193503</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>162972; 222700</t>
+          <t>164194; 223469</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>144468; 203895</t>
+          <t>178967; 221692</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>320501; 391359</t>
+          <t>322344; 392761</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>312392; 385773</t>
+          <t>314701; 389525</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>356596; 431298</t>
+          <t>352398; 433987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>305640; 398063</t>
+          <t>360441; 427257</t>
         </is>
       </c>
     </row>
